--- a/ShortTimeTests/datas/testData.xlsx
+++ b/ShortTimeTests/datas/testData.xlsx
@@ -8,25 +8,34 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VsCode\Workspace\CellScript\ShortTimeTests\datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE860804-B20B-449C-9A53-A86D181DE6FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16636C05-6CD0-4763-9F86-28B864D6241A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
     <sheet name="FillEmptyUp" sheetId="1" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="98">
   <si>
     <t>PICTURE</t>
   </si>
@@ -321,6 +330,10 @@
   </si>
   <si>
     <t>Red</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FormatText</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -328,6 +341,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="177" formatCode="0&quot;Format&quot;"/>
+  </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -364,13 +380,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <numFmt numFmtId="177" formatCode="0&quot;Format&quot;"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -384,12 +405,15 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{8FA2ACCF-6189-47F5-8D45-04BD32E69996}" name="Table1" displayName="Table1" ref="A1:C6" totalsRowShown="0">
-  <autoFilter ref="A1:C6" xr:uid="{8FA2ACCF-6189-47F5-8D45-04BD32E69996}"/>
-  <tableColumns count="3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{8FA2ACCF-6189-47F5-8D45-04BD32E69996}" name="Table1" displayName="Table1" ref="A1:D6" totalsRowShown="0">
+  <autoFilter ref="A1:D6" xr:uid="{8FA2ACCF-6189-47F5-8D45-04BD32E69996}"/>
+  <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{A23DE071-6EA2-49BB-9885-30C680BEF517}" name="Art"/>
     <tableColumn id="2" xr3:uid="{6CD1895F-C851-4969-8208-24CDC06A8DE8}" name="Color"/>
     <tableColumn id="3" xr3:uid="{D35D52F4-1688-435D-BFB8-780AC0C37D18}" name="Size"/>
+    <tableColumn id="4" xr3:uid="{9B3894DB-5F4B-4D9A-A79C-D5769380C6B3}" name="FormatText" dataDxfId="0">
+      <calculatedColumnFormula>0</calculatedColumnFormula>
+    </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -658,10 +682,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32BF126F-EA4B-4E42-8D6F-5092BF56D9C1}">
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="4" max="4" width="19.1640625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>92</v>
       </c>
@@ -671,8 +698,11 @@
       <c r="C1" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>95</v>
       </c>
@@ -682,8 +712,12 @@
       <c r="C2">
         <v>6</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D2" s="1">
+        <f>0</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>95</v>
       </c>
@@ -693,8 +727,12 @@
       <c r="C3">
         <v>7</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D3" s="1">
+        <f>0</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>95</v>
       </c>
@@ -704,8 +742,12 @@
       <c r="C4">
         <v>8</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D4" s="1">
+        <f>0</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>95</v>
       </c>
@@ -715,8 +757,12 @@
       <c r="C5">
         <v>9</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D5" s="1">
+        <f>0</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>95</v>
       </c>
@@ -725,6 +771,10 @@
       </c>
       <c r="C6">
         <v>10</v>
+      </c>
+      <c r="D6" s="1">
+        <f>0</f>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -740,9 +790,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:U50"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -783,7 +833,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
       <c r="Q2" t="s">
         <v>13</v>
       </c>
@@ -794,7 +844,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>16</v>
       </c>
@@ -856,7 +906,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
       <c r="E4" t="s">
         <v>22</v>
       </c>
@@ -882,7 +932,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
       <c r="E5" t="s">
         <v>23</v>
       </c>
@@ -908,7 +958,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>24</v>
       </c>
@@ -970,7 +1020,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
       <c r="E7" t="s">
         <v>29</v>
       </c>
@@ -996,7 +1046,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
       <c r="E8" t="s">
         <v>30</v>
       </c>
@@ -1022,7 +1072,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
         <v>31</v>
       </c>
@@ -1084,7 +1134,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
       <c r="E10" t="s">
         <v>35</v>
       </c>
@@ -1110,7 +1160,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
       <c r="E11" t="s">
         <v>36</v>
       </c>
@@ -1136,7 +1186,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
         <v>37</v>
       </c>
@@ -1198,7 +1248,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
       <c r="E13" t="s">
         <v>34</v>
       </c>
@@ -1224,7 +1274,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
       <c r="E14" t="s">
         <v>40</v>
       </c>
@@ -1250,7 +1300,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
         <v>41</v>
       </c>
@@ -1312,7 +1362,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
       <c r="E16" t="s">
         <v>45</v>
       </c>
@@ -1338,7 +1388,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:21" x14ac:dyDescent="0.3">
       <c r="E17" t="s">
         <v>46</v>
       </c>
@@ -1364,7 +1414,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
         <v>47</v>
       </c>
@@ -1426,7 +1476,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="19" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:21" x14ac:dyDescent="0.3">
       <c r="E19" t="s">
         <v>51</v>
       </c>
@@ -1452,7 +1502,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:21" x14ac:dyDescent="0.3">
       <c r="E20" t="s">
         <v>52</v>
       </c>
@@ -1478,7 +1528,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B21" t="s">
         <v>53</v>
       </c>
@@ -1540,7 +1590,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="22" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:21" x14ac:dyDescent="0.3">
       <c r="E22" t="s">
         <v>56</v>
       </c>
@@ -1566,7 +1616,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="23" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:21" x14ac:dyDescent="0.3">
       <c r="E23" t="s">
         <v>57</v>
       </c>
@@ -1592,7 +1642,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="24" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B24" t="s">
         <v>58</v>
       </c>
@@ -1654,7 +1704,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="25" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:21" x14ac:dyDescent="0.3">
       <c r="E25" t="s">
         <v>63</v>
       </c>
@@ -1680,7 +1730,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="26" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:21" x14ac:dyDescent="0.3">
       <c r="E26" t="s">
         <v>64</v>
       </c>
@@ -1706,7 +1756,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="27" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B27" t="s">
         <v>58</v>
       </c>
@@ -1768,7 +1818,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="28" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:21" x14ac:dyDescent="0.3">
       <c r="E28" t="s">
         <v>63</v>
       </c>
@@ -1794,7 +1844,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="29" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:21" x14ac:dyDescent="0.3">
       <c r="E29" t="s">
         <v>64</v>
       </c>
@@ -1820,7 +1870,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="30" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B30" t="s">
         <v>67</v>
       </c>
@@ -1882,7 +1932,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="31" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:21" x14ac:dyDescent="0.3">
       <c r="E31" t="s">
         <v>71</v>
       </c>
@@ -1908,7 +1958,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="32" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:21" x14ac:dyDescent="0.3">
       <c r="E32" t="s">
         <v>72</v>
       </c>
@@ -1934,7 +1984,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="33" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B33" t="s">
         <v>67</v>
       </c>
@@ -1996,7 +2046,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="34" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:21" x14ac:dyDescent="0.3">
       <c r="E34" t="s">
         <v>71</v>
       </c>
@@ -2022,7 +2072,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="35" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:21" x14ac:dyDescent="0.3">
       <c r="E35" t="s">
         <v>72</v>
       </c>
@@ -2048,7 +2098,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="36" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B36" t="s">
         <v>75</v>
       </c>
@@ -2110,7 +2160,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="37" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:21" x14ac:dyDescent="0.3">
       <c r="E37" t="s">
         <v>78</v>
       </c>
@@ -2136,7 +2186,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="38" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:21" x14ac:dyDescent="0.3">
       <c r="E38" t="s">
         <v>61</v>
       </c>
@@ -2162,7 +2212,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="39" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B39" t="s">
         <v>79</v>
       </c>
@@ -2224,7 +2274,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="40" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:21" x14ac:dyDescent="0.3">
       <c r="E40" t="s">
         <v>78</v>
       </c>
@@ -2250,7 +2300,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="41" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:21" x14ac:dyDescent="0.3">
       <c r="E41" t="s">
         <v>46</v>
       </c>
@@ -2276,7 +2326,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="42" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B42" t="s">
         <v>82</v>
       </c>
@@ -2338,7 +2388,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="43" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:21" x14ac:dyDescent="0.3">
       <c r="E43" t="s">
         <v>45</v>
       </c>
@@ -2364,7 +2414,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="44" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:21" x14ac:dyDescent="0.3">
       <c r="E44" t="s">
         <v>46</v>
       </c>
@@ -2390,7 +2440,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="45" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B45" t="s">
         <v>86</v>
       </c>
@@ -2452,7 +2502,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="46" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:21" x14ac:dyDescent="0.3">
       <c r="E46" t="s">
         <v>61</v>
       </c>
@@ -2478,7 +2528,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="47" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:21" x14ac:dyDescent="0.3">
       <c r="E47" t="s">
         <v>78</v>
       </c>
@@ -2504,7 +2554,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="48" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B48" t="s">
         <v>89</v>
       </c>
@@ -2566,7 +2616,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="49" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="49" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E49" t="s">
         <v>78</v>
       </c>
@@ -2592,7 +2642,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="50" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="50" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E50" t="s">
         <v>45</v>
       </c>
